--- a/2026.01.15_Загрузочный датасет четкий MoSCoW_группа экспертов_с_итогом.xlsx
+++ b/2026.01.15_Загрузочный датасет четкий MoSCoW_группа экспертов_с_итогом.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\79147\Documents\Документы, инвестиции, личные финансы\2024.07.03_Альфа-банк\Магистратура ВШЭ\20_Магистерская диссертация\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3E61B88-9165-408E-8820-E20E5B65A502}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EA1FADB-3DF4-40D1-B41A-AC7250487C42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="815" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,12 +18,12 @@
     <sheet name="Четкий MoSCoW_эксперт 3" sheetId="3" r:id="rId3"/>
     <sheet name="Приоритизация_итог" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="36">
   <si>
     <t>Эксперт 1</t>
   </si>
@@ -97,7 +97,10 @@
     <t>Эксперт</t>
   </si>
   <si>
-    <t>Вес</t>
+    <t>Вес_raw</t>
+  </si>
+  <si>
+    <t>Вес_norm</t>
   </si>
   <si>
     <t>Четкий MoSCoW_эксперт 1</t>
@@ -109,22 +112,25 @@
     <t>Четкий MoSCoW_эксперт 3</t>
   </si>
   <si>
+    <t>SUM</t>
+  </si>
+  <si>
     <t>Rank</t>
   </si>
   <si>
     <t>FR</t>
   </si>
   <si>
+    <t>PFR_Четкий MoSCoW_эксперт 1</t>
+  </si>
+  <si>
+    <t>PFR_Четкий MoSCoW_эксперт 2</t>
+  </si>
+  <si>
+    <t>PFR_Четкий MoSCoW_эксперт 3</t>
+  </si>
+  <si>
     <t>PFR_group</t>
-  </si>
-  <si>
-    <t>PFR_Четкий MoSCoW_эксперт 1</t>
-  </si>
-  <si>
-    <t>PFR_Четкий MoSCoW_эксперт 2</t>
-  </si>
-  <si>
-    <t>PFR_Четкий MoSCoW_эксперт 3</t>
   </si>
 </sst>
 </file>
@@ -160,8 +166,6 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="204"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1197,9 +1201,9 @@
   <dimension ref="A1:F17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="30.140625" customWidth="1"/>
-    <col min="2" max="3" width="12" customWidth="1"/>
-    <col min="4" max="6" width="29" customWidth="1"/>
+    <col min="1" max="1" width="25.28515625" customWidth="1"/>
+    <col min="2" max="2" width="14" customWidth="1"/>
+    <col min="3" max="6" width="30" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1209,49 +1213,72 @@
       <c r="B1" s="8" t="s">
         <v>24</v>
       </c>
+      <c r="C1" s="8" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B2">
+        <v>0.75</v>
+      </c>
+      <c r="C2">
         <v>0.3</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B3">
+        <v>0.75</v>
+      </c>
+      <c r="C3">
         <v>0.3</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4">
         <v>0.4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="B5" s="8">
+        <v>2.5</v>
+      </c>
+      <c r="C5" s="8">
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -1262,16 +1289,16 @@
         <v>11</v>
       </c>
       <c r="C8">
+        <v>14.15</v>
+      </c>
+      <c r="D8">
+        <v>12.425000000000001</v>
+      </c>
+      <c r="E8">
+        <v>11.625</v>
+      </c>
+      <c r="F8">
         <v>12.622999999999999</v>
-      </c>
-      <c r="D8">
-        <v>14.15</v>
-      </c>
-      <c r="E8">
-        <v>12.425000000000001</v>
-      </c>
-      <c r="F8">
-        <v>11.625</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -1282,16 +1309,16 @@
         <v>13</v>
       </c>
       <c r="C9">
+        <v>9.9</v>
+      </c>
+      <c r="D9">
+        <v>15.75</v>
+      </c>
+      <c r="E9">
+        <v>11.6</v>
+      </c>
+      <c r="F9">
         <v>12.335000000000001</v>
-      </c>
-      <c r="D9">
-        <v>9.9</v>
-      </c>
-      <c r="E9">
-        <v>15.75</v>
-      </c>
-      <c r="F9">
-        <v>11.6</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -1302,16 +1329,16 @@
         <v>18</v>
       </c>
       <c r="C10">
+        <v>12.45</v>
+      </c>
+      <c r="D10">
+        <v>12.425000000000001</v>
+      </c>
+      <c r="E10">
+        <v>10.8</v>
+      </c>
+      <c r="F10">
         <v>11.782</v>
-      </c>
-      <c r="D10">
-        <v>12.45</v>
-      </c>
-      <c r="E10">
-        <v>12.425000000000001</v>
-      </c>
-      <c r="F10">
-        <v>10.8</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -1322,16 +1349,16 @@
         <v>15</v>
       </c>
       <c r="C11">
+        <v>10.75</v>
+      </c>
+      <c r="D11">
+        <v>15.75</v>
+      </c>
+      <c r="E11">
+        <v>9.125</v>
+      </c>
+      <c r="F11">
         <v>11.6</v>
-      </c>
-      <c r="D11">
-        <v>10.75</v>
-      </c>
-      <c r="E11">
-        <v>15.75</v>
-      </c>
-      <c r="F11">
-        <v>9.125</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -1342,16 +1369,16 @@
         <v>14</v>
       </c>
       <c r="C12">
+        <v>12.45</v>
+      </c>
+      <c r="D12">
+        <v>14.1</v>
+      </c>
+      <c r="E12">
+        <v>8.2750000000000004</v>
+      </c>
+      <c r="F12">
         <v>11.275</v>
-      </c>
-      <c r="D12">
-        <v>12.45</v>
-      </c>
-      <c r="E12">
-        <v>14.1</v>
-      </c>
-      <c r="F12">
-        <v>8.2750000000000004</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -1362,16 +1389,16 @@
         <v>19</v>
       </c>
       <c r="C13">
+        <v>10.75</v>
+      </c>
+      <c r="D13">
+        <v>13.275</v>
+      </c>
+      <c r="E13">
+        <v>9.125</v>
+      </c>
+      <c r="F13">
         <v>10.856999999999999</v>
-      </c>
-      <c r="D13">
-        <v>10.75</v>
-      </c>
-      <c r="E13">
-        <v>13.275</v>
-      </c>
-      <c r="F13">
-        <v>9.125</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -1382,16 +1409,16 @@
         <v>17</v>
       </c>
       <c r="C14">
+        <v>10.8</v>
+      </c>
+      <c r="D14">
+        <v>14.1</v>
+      </c>
+      <c r="E14">
+        <v>8.2750000000000004</v>
+      </c>
+      <c r="F14">
         <v>10.78</v>
-      </c>
-      <c r="D14">
-        <v>10.8</v>
-      </c>
-      <c r="E14">
-        <v>14.1</v>
-      </c>
-      <c r="F14">
-        <v>8.2750000000000004</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -1402,13 +1429,13 @@
         <v>20</v>
       </c>
       <c r="C15">
+        <v>8.2750000000000004</v>
+      </c>
+      <c r="D15">
+        <v>13.275</v>
+      </c>
+      <c r="E15">
         <v>10.775</v>
-      </c>
-      <c r="D15">
-        <v>8.2750000000000004</v>
-      </c>
-      <c r="E15">
-        <v>13.275</v>
       </c>
       <c r="F15">
         <v>10.775</v>
@@ -1422,16 +1449,16 @@
         <v>16</v>
       </c>
       <c r="C16">
+        <v>10.8</v>
+      </c>
+      <c r="D16">
+        <v>14.1</v>
+      </c>
+      <c r="E16">
+        <v>6.6</v>
+      </c>
+      <c r="F16">
         <v>10.11</v>
-      </c>
-      <c r="D16">
-        <v>10.8</v>
-      </c>
-      <c r="E16">
-        <v>14.1</v>
-      </c>
-      <c r="F16">
-        <v>6.6</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -1442,16 +1469,16 @@
         <v>12</v>
       </c>
       <c r="C17">
+        <v>6.6</v>
+      </c>
+      <c r="D17">
+        <v>8.25</v>
+      </c>
+      <c r="E17">
+        <v>5.7750000000000004</v>
+      </c>
+      <c r="F17">
         <v>6.7649999999999997</v>
-      </c>
-      <c r="D17">
-        <v>6.6</v>
-      </c>
-      <c r="E17">
-        <v>8.25</v>
-      </c>
-      <c r="F17">
-        <v>5.7750000000000004</v>
       </c>
     </row>
   </sheetData>
